--- a/data/trans_orig/P36B01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B01-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de café o té en 2016</t>
+          <t>Población según la frecuencia de consumo de café o té en 2016 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34594</t>
+          <t>34659</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61391</t>
+          <t>61589</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21973</t>
+          <t>22953</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45306</t>
+          <t>47029</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62666</t>
+          <t>63700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98557</t>
+          <t>97458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10627</t>
+          <t>11487</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17299</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17417</t>
+          <t>16362</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>15832</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>10963</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28655</t>
+          <t>29226</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16140</t>
+          <t>16549</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18304</t>
+          <t>20589</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10899</t>
+          <t>9832</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29176</t>
+          <t>27985</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>343383</t>
+          <t>343076</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>374638</t>
+          <t>374576</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>273927</t>
+          <t>272812</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>300966</t>
+          <t>301922</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>625034</t>
+          <t>627523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>668995</t>
+          <t>668052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,41%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53231</t>
+          <t>52039</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22761</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43926</t>
+          <t>44801</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56363</t>
+          <t>56047</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89205</t>
+          <t>88945</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>963</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14057</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,42 +1658,42 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>5950</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2748</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>13218</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>1,61%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5950</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>12780</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15177</t>
+          <t>14308</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>15546</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21928</t>
+          <t>22457</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>307849</t>
+          <t>309127</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>336516</t>
+          <t>336662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>309135</t>
+          <t>309254</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>334455</t>
+          <t>334109</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>626499</t>
+          <t>629202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>664927</t>
+          <t>664542</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>52053</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82610</t>
+          <t>82036</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22554</t>
+          <t>22415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63493</t>
+          <t>64398</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97523</t>
+          <t>98426</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16713</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>18296</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21387</t>
+          <t>21607</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>23577</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>12324</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>17151</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>410920</t>
+          <t>410778</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>445734</t>
+          <t>446629</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>137784</t>
+          <t>137345</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>153493</t>
+          <t>153926</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>555502</t>
+          <t>555561</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>594706</t>
+          <t>594679</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,55%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118688</t>
+          <t>118803</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166949</t>
+          <t>164702</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>82360</t>
+          <t>82505</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>120981</t>
+          <t>121134</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>211793</t>
+          <t>214390</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>270751</t>
+          <t>272078</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10155</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27202</t>
+          <t>27320</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9601</t>
+          <t>9635</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24369</t>
+          <t>25599</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,47 +2939,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>32918</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>22896</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>44602</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>32918</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>22467</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>47002</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20328</t>
+          <t>20636</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20882</t>
+          <t>21678</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16057</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>35297</t>
+          <t>36280</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25507</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49111</t>
+          <t>48666</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19377</t>
+          <t>19192</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32445</t>
+          <t>33157</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60971</t>
+          <t>60774</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>911882</t>
+          <t>914303</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>966634</t>
+          <t>967315</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>663036</t>
+          <t>662748</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>707337</t>
+          <t>705873</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1594493</t>
+          <t>1592248</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1665163</t>
+          <t>1658771</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,09%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>85283</t>
+          <t>83747</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>122466</t>
+          <t>121553</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>66654</t>
+          <t>66479</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>100859</t>
+          <t>101170</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>160067</t>
+          <t>161238</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>214412</t>
+          <t>211770</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>8246</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24236</t>
+          <t>23888</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19400</t>
+          <t>19164</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37180</t>
+          <t>36171</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14559</t>
+          <t>14461</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11310</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>21148</t>
+          <t>22231</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20265</t>
+          <t>22588</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17437</t>
+          <t>17870</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>30977</t>
+          <t>32438</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>462334</t>
+          <t>462299</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>506177</t>
+          <t>504370</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>610750</t>
+          <t>610735</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>648310</t>
+          <t>648163</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1083432</t>
+          <t>1084136</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1141983</t>
+          <t>1141313</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,04%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>62962</t>
+          <t>63604</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>93041</t>
+          <t>93293</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>164110</t>
+          <t>166897</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>217438</t>
+          <t>216751</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>239614</t>
+          <t>238482</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>298500</t>
+          <t>297667</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>23612</t>
+          <t>24051</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>23429</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,47 +4303,47 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>27133</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>17709</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>39595</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
           <t>1,99%</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>27133</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>18115</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>38927</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>19022</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>39085</t>
+          <t>40122</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>12551</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>31280</t>
+          <t>31502</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>34736</t>
+          <t>35885</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>64254</t>
+          <t>62329</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>21298</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>23995</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>47689</t>
+          <t>47108</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>34826</t>
+          <t>35260</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>61732</t>
+          <t>62479</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>136649</t>
+          <t>137972</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>171920</t>
+          <t>172596</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>792485</t>
+          <t>791571</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>852206</t>
+          <t>848044</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>939498</t>
+          <t>942686</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1007452</t>
+          <t>1011333</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,05%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>431366</t>
+          <t>429896</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>512559</t>
+          <t>510093</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>410473</t>
+          <t>412806</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>488536</t>
+          <t>493692</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>867161</t>
+          <t>870463</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>980844</t>
+          <t>987034</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>50482</t>
+          <t>48651</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>83100</t>
+          <t>80652</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>36420</t>
+          <t>34973</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>62796</t>
+          <t>62889</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>91296</t>
+          <t>92191</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>133839</t>
+          <t>134147</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>56520</t>
+          <t>54970</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>90025</t>
+          <t>91974</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>41479</t>
+          <t>40943</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>70394</t>
+          <t>68778</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>103078</t>
+          <t>103211</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>146103</t>
+          <t>148058</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>66030</t>
+          <t>66251</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>102738</t>
+          <t>101157</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>55871</t>
+          <t>55609</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>90501</t>
+          <t>91232</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>129089</t>
+          <t>130891</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>180015</t>
+          <t>179687</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2646801</t>
+          <t>2646886</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2736053</t>
+          <t>2742623</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2851187</t>
+          <t>2847020</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2939822</t>
+          <t>2938321</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>5529686</t>
+          <t>5521492</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5652211</t>
+          <t>5648681</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B01-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34659</t>
+          <t>34763</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61589</t>
+          <t>60167</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22953</t>
+          <t>22787</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47029</t>
+          <t>46230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63700</t>
+          <t>63412</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97458</t>
+          <t>98595</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16362</t>
+          <t>17471</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15832</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10963</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29226</t>
+          <t>27808</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>16412</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20589</t>
+          <t>17910</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9832</t>
+          <t>10838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27985</t>
+          <t>28546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>343076</t>
+          <t>342593</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>374576</t>
+          <t>373845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>272812</t>
+          <t>274090</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>301922</t>
+          <t>300573</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>627523</t>
+          <t>626978</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>668052</t>
+          <t>668113</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>27706</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52039</t>
+          <t>53756</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>23095</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44801</t>
+          <t>43549</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56047</t>
+          <t>55705</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88945</t>
+          <t>87854</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>9549</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>6820</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13218</t>
+          <t>12005</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14308</t>
+          <t>15086</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15546</t>
+          <t>16082</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22457</t>
+          <t>21958</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>309127</t>
+          <t>307605</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>336662</t>
+          <t>336048</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>309254</t>
+          <t>310679</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>334109</t>
+          <t>336353</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>629202</t>
+          <t>626562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>664542</t>
+          <t>663762</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52053</t>
+          <t>50936</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82036</t>
+          <t>81664</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>8419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22415</t>
+          <t>23322</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64398</t>
+          <t>64838</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98426</t>
+          <t>99034</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15888</t>
+          <t>16200</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18296</t>
+          <t>17499</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21607</t>
+          <t>24042</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>5654</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23577</t>
+          <t>23681</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12324</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17151</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>410778</t>
+          <t>409342</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>446629</t>
+          <t>446215</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>137345</t>
+          <t>137284</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>153926</t>
+          <t>154045</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>555561</t>
+          <t>553304</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>594679</t>
+          <t>592950</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,3%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118803</t>
+          <t>118367</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>164702</t>
+          <t>163747</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>82505</t>
+          <t>83816</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>121134</t>
+          <t>122556</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>214390</t>
+          <t>213568</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>272078</t>
+          <t>271492</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27320</t>
+          <t>27489</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>8743</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25599</t>
+          <t>23792</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,47 +2939,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>32918</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>23151</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>45862</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>32918</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>22896</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>44602</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20636</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21678</t>
+          <t>23444</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16261</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36280</t>
+          <t>35709</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48666</t>
+          <t>49524</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19192</t>
+          <t>18069</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33157</t>
+          <t>33614</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60774</t>
+          <t>60813</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>914303</t>
+          <t>916700</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>967315</t>
+          <t>968359</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>662748</t>
+          <t>659993</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>705873</t>
+          <t>703932</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1592248</t>
+          <t>1595122</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1658771</t>
+          <t>1662814</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>83747</t>
+          <t>85657</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>121553</t>
+          <t>119939</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>66479</t>
+          <t>67178</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>101170</t>
+          <t>101278</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>161238</t>
+          <t>161546</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>211770</t>
+          <t>209359</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23888</t>
+          <t>23635</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>20405</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16120</t>
+          <t>16148</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>36171</t>
+          <t>36997</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>22231</t>
+          <t>21857</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22588</t>
+          <t>19677</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17870</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>32274</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>462299</t>
+          <t>462487</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>504370</t>
+          <t>503347</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>610735</t>
+          <t>608770</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>648163</t>
+          <t>647402</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1084136</t>
+          <t>1085986</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1141313</t>
+          <t>1142340</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,12%</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>63604</t>
+          <t>61507</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>93293</t>
+          <t>92956</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>166897</t>
+          <t>166553</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>216751</t>
+          <t>215849</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>238482</t>
+          <t>236445</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>297667</t>
+          <t>297469</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>24051</t>
+          <t>23945</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>21723</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>18951</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>39595</t>
+          <t>39537</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>18284</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>40122</t>
+          <t>39839</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>31502</t>
+          <t>31224</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>35885</t>
+          <t>35877</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>62329</t>
+          <t>64817</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>21298</t>
+          <t>21871</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>23293</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>47108</t>
+          <t>48292</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>35260</t>
+          <t>35226</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>62479</t>
+          <t>62706</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>137972</t>
+          <t>139293</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>172596</t>
+          <t>173539</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>791571</t>
+          <t>793273</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>848044</t>
+          <t>848430</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>942686</t>
+          <t>938643</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1011333</t>
+          <t>1009873</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,94%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>429896</t>
+          <t>432288</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>510093</t>
+          <t>516721</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>412806</t>
+          <t>412811</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>493692</t>
+          <t>494959</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>870463</t>
+          <t>868604</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>987034</t>
+          <t>986253</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>48651</t>
+          <t>49460</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>80652</t>
+          <t>81093</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>34973</t>
+          <t>36910</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>62889</t>
+          <t>63498</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>92191</t>
+          <t>93994</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>134147</t>
+          <t>135421</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>54970</t>
+          <t>54682</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>91974</t>
+          <t>89690</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>40943</t>
+          <t>40023</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>68778</t>
+          <t>70149</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>103211</t>
+          <t>103824</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>148058</t>
+          <t>146710</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>66251</t>
+          <t>64972</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>101157</t>
+          <t>104184</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>55609</t>
+          <t>56548</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>91232</t>
+          <t>90663</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>130891</t>
+          <t>130212</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>179687</t>
+          <t>179658</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2646886</t>
+          <t>2644076</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2742623</t>
+          <t>2740602</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2847020</t>
+          <t>2848152</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2938321</t>
+          <t>2939666</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>5521492</t>
+          <t>5520643</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5648681</t>
+          <t>5649565</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,85%</t>
         </is>
       </c>
     </row>
